--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568898</v>
+        <v>121568876</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762944</v>
+        <v>762743</v>
       </c>
       <c r="R2" t="n">
-        <v>7117656</v>
+        <v>7117540</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568877</v>
+        <v>121568894</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762732</v>
+        <v>762831</v>
       </c>
       <c r="R3" t="n">
-        <v>7117536</v>
+        <v>7117638</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568894</v>
+        <v>121568897</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762831</v>
+        <v>762908</v>
       </c>
       <c r="R4" t="n">
-        <v>7117638</v>
+        <v>7117644</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568875</v>
+        <v>121568872</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762784</v>
+        <v>762842</v>
       </c>
       <c r="R5" t="n">
-        <v>7117549</v>
+        <v>7117580</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568895</v>
+        <v>121568893</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762857</v>
+        <v>762816</v>
       </c>
       <c r="R6" t="n">
-        <v>7117643</v>
+        <v>7117667</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568871</v>
+        <v>121568877</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762884</v>
+        <v>762732</v>
       </c>
       <c r="R7" t="n">
-        <v>7117590</v>
+        <v>7117536</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568872</v>
+        <v>121568898</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762842</v>
+        <v>762944</v>
       </c>
       <c r="R8" t="n">
-        <v>7117580</v>
+        <v>7117656</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568873</v>
+        <v>121568871</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762822</v>
+        <v>762884</v>
       </c>
       <c r="R9" t="n">
-        <v>7117550</v>
+        <v>7117590</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568893</v>
+        <v>121568895</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762816</v>
+        <v>762857</v>
       </c>
       <c r="R10" t="n">
-        <v>7117667</v>
+        <v>7117643</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568876</v>
+        <v>121568873</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762743</v>
+        <v>762822</v>
       </c>
       <c r="R11" t="n">
-        <v>7117540</v>
+        <v>7117550</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568874</v>
+        <v>121568875</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762800</v>
+        <v>762784</v>
       </c>
       <c r="R12" t="n">
-        <v>7117547</v>
+        <v>7117549</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568897</v>
+        <v>121568874</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762908</v>
+        <v>762800</v>
       </c>
       <c r="R13" t="n">
-        <v>7117644</v>
+        <v>7117547</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568876</v>
+        <v>121568874</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762743</v>
+        <v>762800</v>
       </c>
       <c r="R2" t="n">
-        <v>7117540</v>
+        <v>7117547</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568894</v>
+        <v>121568895</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762831</v>
+        <v>762857</v>
       </c>
       <c r="R3" t="n">
-        <v>7117638</v>
+        <v>7117643</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568872</v>
+        <v>121568876</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762842</v>
+        <v>762743</v>
       </c>
       <c r="R5" t="n">
-        <v>7117580</v>
+        <v>7117540</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568893</v>
+        <v>121568875</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762816</v>
+        <v>762784</v>
       </c>
       <c r="R6" t="n">
-        <v>7117667</v>
+        <v>7117549</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568877</v>
+        <v>121568871</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762732</v>
+        <v>762884</v>
       </c>
       <c r="R7" t="n">
-        <v>7117536</v>
+        <v>7117590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568898</v>
+        <v>121568893</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762944</v>
+        <v>762816</v>
       </c>
       <c r="R8" t="n">
-        <v>7117656</v>
+        <v>7117667</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568871</v>
+        <v>121568898</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762884</v>
+        <v>762944</v>
       </c>
       <c r="R9" t="n">
-        <v>7117590</v>
+        <v>7117656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568895</v>
+        <v>121568872</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762857</v>
+        <v>762842</v>
       </c>
       <c r="R10" t="n">
-        <v>7117643</v>
+        <v>7117580</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568873</v>
+        <v>121568877</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762822</v>
+        <v>762732</v>
       </c>
       <c r="R11" t="n">
-        <v>7117550</v>
+        <v>7117536</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568875</v>
+        <v>121568894</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762784</v>
+        <v>762831</v>
       </c>
       <c r="R12" t="n">
-        <v>7117549</v>
+        <v>7117638</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568874</v>
+        <v>121568873</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762800</v>
+        <v>762822</v>
       </c>
       <c r="R13" t="n">
-        <v>7117547</v>
+        <v>7117550</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568874</v>
+        <v>121568893</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762800</v>
+        <v>762816</v>
       </c>
       <c r="R2" t="n">
-        <v>7117547</v>
+        <v>7117667</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568895</v>
+        <v>121568871</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762857</v>
+        <v>762884</v>
       </c>
       <c r="R3" t="n">
-        <v>7117643</v>
+        <v>7117590</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568897</v>
+        <v>121568873</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762908</v>
+        <v>762822</v>
       </c>
       <c r="R4" t="n">
-        <v>7117644</v>
+        <v>7117550</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568876</v>
+        <v>121568895</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762743</v>
+        <v>762857</v>
       </c>
       <c r="R5" t="n">
-        <v>7117540</v>
+        <v>7117643</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568875</v>
+        <v>121568872</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762784</v>
+        <v>762842</v>
       </c>
       <c r="R6" t="n">
-        <v>7117549</v>
+        <v>7117580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568871</v>
+        <v>121568877</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762884</v>
+        <v>762732</v>
       </c>
       <c r="R7" t="n">
-        <v>7117590</v>
+        <v>7117536</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568893</v>
+        <v>121568874</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762816</v>
+        <v>762800</v>
       </c>
       <c r="R8" t="n">
-        <v>7117667</v>
+        <v>7117547</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568898</v>
+        <v>121568875</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762944</v>
+        <v>762784</v>
       </c>
       <c r="R9" t="n">
-        <v>7117656</v>
+        <v>7117549</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568872</v>
+        <v>121568876</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762842</v>
+        <v>762743</v>
       </c>
       <c r="R10" t="n">
-        <v>7117580</v>
+        <v>7117540</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568877</v>
+        <v>121568898</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762732</v>
+        <v>762944</v>
       </c>
       <c r="R11" t="n">
-        <v>7117536</v>
+        <v>7117656</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568873</v>
+        <v>121568897</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762822</v>
+        <v>762908</v>
       </c>
       <c r="R13" t="n">
-        <v>7117550</v>
+        <v>7117644</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568893</v>
+        <v>121568897</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762816</v>
+        <v>762908</v>
       </c>
       <c r="R2" t="n">
-        <v>7117667</v>
+        <v>7117644</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568871</v>
+        <v>121568873</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762884</v>
+        <v>762822</v>
       </c>
       <c r="R3" t="n">
-        <v>7117590</v>
+        <v>7117550</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568873</v>
+        <v>121568895</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762822</v>
+        <v>762857</v>
       </c>
       <c r="R4" t="n">
-        <v>7117550</v>
+        <v>7117643</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568895</v>
+        <v>121568874</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762857</v>
+        <v>762800</v>
       </c>
       <c r="R5" t="n">
-        <v>7117643</v>
+        <v>7117547</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568877</v>
+        <v>121568876</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762732</v>
+        <v>762743</v>
       </c>
       <c r="R7" t="n">
-        <v>7117536</v>
+        <v>7117540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568874</v>
+        <v>121568877</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762800</v>
+        <v>762732</v>
       </c>
       <c r="R8" t="n">
-        <v>7117547</v>
+        <v>7117536</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568875</v>
+        <v>121568871</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762784</v>
+        <v>762884</v>
       </c>
       <c r="R9" t="n">
-        <v>7117549</v>
+        <v>7117590</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568876</v>
+        <v>121568893</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762743</v>
+        <v>762816</v>
       </c>
       <c r="R10" t="n">
-        <v>7117540</v>
+        <v>7117667</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568898</v>
+        <v>121568875</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762944</v>
+        <v>762784</v>
       </c>
       <c r="R11" t="n">
-        <v>7117656</v>
+        <v>7117549</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568897</v>
+        <v>121568898</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762908</v>
+        <v>762944</v>
       </c>
       <c r="R13" t="n">
-        <v>7117644</v>
+        <v>7117656</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568871</v>
+        <v>121568894</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762884</v>
+        <v>762831</v>
       </c>
       <c r="R2" t="n">
-        <v>7117590</v>
+        <v>7117638</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568877</v>
+        <v>121568875</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762732</v>
+        <v>762784</v>
       </c>
       <c r="R3" t="n">
-        <v>7117536</v>
+        <v>7117549</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568874</v>
+        <v>121568871</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762800</v>
+        <v>762884</v>
       </c>
       <c r="R4" t="n">
-        <v>7117547</v>
+        <v>7117590</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568894</v>
+        <v>121568873</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762831</v>
+        <v>762822</v>
       </c>
       <c r="R5" t="n">
-        <v>7117638</v>
+        <v>7117550</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568873</v>
+        <v>121568874</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762822</v>
+        <v>762800</v>
       </c>
       <c r="R6" t="n">
-        <v>7117550</v>
+        <v>7117547</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568876</v>
+        <v>121568893</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762743</v>
+        <v>762816</v>
       </c>
       <c r="R7" t="n">
-        <v>7117540</v>
+        <v>7117667</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568872</v>
+        <v>121568897</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762842</v>
+        <v>762908</v>
       </c>
       <c r="R8" t="n">
-        <v>7117580</v>
+        <v>7117644</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568893</v>
+        <v>121568877</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762816</v>
+        <v>762732</v>
       </c>
       <c r="R9" t="n">
-        <v>7117667</v>
+        <v>7117536</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568875</v>
+        <v>121568895</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762784</v>
+        <v>762857</v>
       </c>
       <c r="R10" t="n">
-        <v>7117549</v>
+        <v>7117643</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568895</v>
+        <v>121568876</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762857</v>
+        <v>762743</v>
       </c>
       <c r="R12" t="n">
-        <v>7117643</v>
+        <v>7117540</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568897</v>
+        <v>121568872</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762908</v>
+        <v>762842</v>
       </c>
       <c r="R13" t="n">
-        <v>7117644</v>
+        <v>7117580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568894</v>
+        <v>121568872</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762831</v>
+        <v>762842</v>
       </c>
       <c r="R2" t="n">
-        <v>7117638</v>
+        <v>7117580</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568875</v>
+        <v>121568876</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762784</v>
+        <v>762743</v>
       </c>
       <c r="R3" t="n">
-        <v>7117549</v>
+        <v>7117540</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568871</v>
+        <v>121568874</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762884</v>
+        <v>762800</v>
       </c>
       <c r="R4" t="n">
-        <v>7117590</v>
+        <v>7117547</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568873</v>
+        <v>121568898</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762822</v>
+        <v>762944</v>
       </c>
       <c r="R5" t="n">
-        <v>7117550</v>
+        <v>7117656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568874</v>
+        <v>121568895</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762800</v>
+        <v>762857</v>
       </c>
       <c r="R6" t="n">
-        <v>7117547</v>
+        <v>7117643</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568893</v>
+        <v>121568877</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762816</v>
+        <v>762732</v>
       </c>
       <c r="R7" t="n">
-        <v>7117667</v>
+        <v>7117536</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568897</v>
+        <v>121568893</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762908</v>
+        <v>762816</v>
       </c>
       <c r="R8" t="n">
-        <v>7117644</v>
+        <v>7117667</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568877</v>
+        <v>121568894</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762732</v>
+        <v>762831</v>
       </c>
       <c r="R9" t="n">
-        <v>7117536</v>
+        <v>7117638</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568895</v>
+        <v>121568871</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762857</v>
+        <v>762884</v>
       </c>
       <c r="R10" t="n">
-        <v>7117643</v>
+        <v>7117590</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568898</v>
+        <v>121568873</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762944</v>
+        <v>762822</v>
       </c>
       <c r="R11" t="n">
-        <v>7117656</v>
+        <v>7117550</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568876</v>
+        <v>121568875</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762743</v>
+        <v>762784</v>
       </c>
       <c r="R12" t="n">
-        <v>7117540</v>
+        <v>7117549</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568872</v>
+        <v>121568897</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762842</v>
+        <v>762908</v>
       </c>
       <c r="R13" t="n">
-        <v>7117580</v>
+        <v>7117644</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568872</v>
+        <v>121568877</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762842</v>
+        <v>762732</v>
       </c>
       <c r="R2" t="n">
-        <v>7117580</v>
+        <v>7117536</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568876</v>
+        <v>121568893</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762743</v>
+        <v>762816</v>
       </c>
       <c r="R3" t="n">
-        <v>7117540</v>
+        <v>7117667</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568874</v>
+        <v>121568871</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762800</v>
+        <v>762884</v>
       </c>
       <c r="R4" t="n">
-        <v>7117547</v>
+        <v>7117590</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568898</v>
+        <v>121568875</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762944</v>
+        <v>762784</v>
       </c>
       <c r="R5" t="n">
-        <v>7117656</v>
+        <v>7117549</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568895</v>
+        <v>121568897</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762857</v>
+        <v>762908</v>
       </c>
       <c r="R6" t="n">
-        <v>7117643</v>
+        <v>7117644</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568877</v>
+        <v>121568873</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762732</v>
+        <v>762822</v>
       </c>
       <c r="R7" t="n">
-        <v>7117536</v>
+        <v>7117550</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568893</v>
+        <v>121568876</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762816</v>
+        <v>762743</v>
       </c>
       <c r="R8" t="n">
-        <v>7117667</v>
+        <v>7117540</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568894</v>
+        <v>121568874</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762831</v>
+        <v>762800</v>
       </c>
       <c r="R9" t="n">
-        <v>7117638</v>
+        <v>7117547</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568871</v>
+        <v>121568898</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762884</v>
+        <v>762944</v>
       </c>
       <c r="R10" t="n">
-        <v>7117590</v>
+        <v>7117656</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568873</v>
+        <v>121568894</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762822</v>
+        <v>762831</v>
       </c>
       <c r="R11" t="n">
-        <v>7117550</v>
+        <v>7117638</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568875</v>
+        <v>121568895</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762784</v>
+        <v>762857</v>
       </c>
       <c r="R12" t="n">
-        <v>7117549</v>
+        <v>7117643</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568897</v>
+        <v>121568872</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762908</v>
+        <v>762842</v>
       </c>
       <c r="R13" t="n">
-        <v>7117644</v>
+        <v>7117580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568893</v>
+        <v>121568894</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762816</v>
+        <v>762831</v>
       </c>
       <c r="R3" t="n">
-        <v>7117667</v>
+        <v>7117638</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568871</v>
+        <v>121568897</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762884</v>
+        <v>762908</v>
       </c>
       <c r="R4" t="n">
-        <v>7117590</v>
+        <v>7117644</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568875</v>
+        <v>121568872</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762784</v>
+        <v>762842</v>
       </c>
       <c r="R5" t="n">
-        <v>7117549</v>
+        <v>7117580</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568897</v>
+        <v>121568898</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762908</v>
+        <v>762944</v>
       </c>
       <c r="R6" t="n">
-        <v>7117644</v>
+        <v>7117656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568873</v>
+        <v>121568876</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762822</v>
+        <v>762743</v>
       </c>
       <c r="R7" t="n">
-        <v>7117550</v>
+        <v>7117540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568876</v>
+        <v>121568871</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762743</v>
+        <v>762884</v>
       </c>
       <c r="R8" t="n">
-        <v>7117540</v>
+        <v>7117590</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568874</v>
+        <v>121568893</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762800</v>
+        <v>762816</v>
       </c>
       <c r="R9" t="n">
-        <v>7117547</v>
+        <v>7117667</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568898</v>
+        <v>121568895</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762944</v>
+        <v>762857</v>
       </c>
       <c r="R10" t="n">
-        <v>7117656</v>
+        <v>7117643</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568894</v>
+        <v>121568874</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762831</v>
+        <v>762800</v>
       </c>
       <c r="R11" t="n">
-        <v>7117638</v>
+        <v>7117547</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568895</v>
+        <v>121568875</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762857</v>
+        <v>762784</v>
       </c>
       <c r="R12" t="n">
-        <v>7117643</v>
+        <v>7117549</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568872</v>
+        <v>121568873</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762842</v>
+        <v>762822</v>
       </c>
       <c r="R13" t="n">
-        <v>7117580</v>
+        <v>7117550</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568877</v>
+        <v>121568894</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762732</v>
+        <v>762831</v>
       </c>
       <c r="R2" t="n">
-        <v>7117536</v>
+        <v>7117638</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568894</v>
+        <v>121568876</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762831</v>
+        <v>762743</v>
       </c>
       <c r="R3" t="n">
-        <v>7117638</v>
+        <v>7117540</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568897</v>
+        <v>121568874</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762908</v>
+        <v>762800</v>
       </c>
       <c r="R4" t="n">
-        <v>7117644</v>
+        <v>7117547</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568872</v>
+        <v>121568875</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762842</v>
+        <v>762784</v>
       </c>
       <c r="R5" t="n">
-        <v>7117580</v>
+        <v>7117549</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568898</v>
+        <v>121568893</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762944</v>
+        <v>762816</v>
       </c>
       <c r="R6" t="n">
-        <v>7117656</v>
+        <v>7117667</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568876</v>
+        <v>121568871</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762743</v>
+        <v>762884</v>
       </c>
       <c r="R7" t="n">
-        <v>7117540</v>
+        <v>7117590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568871</v>
+        <v>121568872</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762884</v>
+        <v>762842</v>
       </c>
       <c r="R8" t="n">
-        <v>7117590</v>
+        <v>7117580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568893</v>
+        <v>121568897</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762816</v>
+        <v>762908</v>
       </c>
       <c r="R9" t="n">
-        <v>7117667</v>
+        <v>7117644</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568895</v>
+        <v>121568873</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762857</v>
+        <v>762822</v>
       </c>
       <c r="R10" t="n">
-        <v>7117643</v>
+        <v>7117550</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568874</v>
+        <v>121568898</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762800</v>
+        <v>762944</v>
       </c>
       <c r="R11" t="n">
-        <v>7117547</v>
+        <v>7117656</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568875</v>
+        <v>121568877</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762784</v>
+        <v>762732</v>
       </c>
       <c r="R12" t="n">
-        <v>7117549</v>
+        <v>7117536</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568873</v>
+        <v>121568895</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762822</v>
+        <v>762857</v>
       </c>
       <c r="R13" t="n">
-        <v>7117550</v>
+        <v>7117643</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568894</v>
+        <v>121568872</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762831</v>
+        <v>762842</v>
       </c>
       <c r="R2" t="n">
-        <v>7117638</v>
+        <v>7117580</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568876</v>
+        <v>121568875</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762743</v>
+        <v>762784</v>
       </c>
       <c r="R3" t="n">
-        <v>7117540</v>
+        <v>7117549</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568874</v>
+        <v>121568871</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762800</v>
+        <v>762884</v>
       </c>
       <c r="R4" t="n">
-        <v>7117547</v>
+        <v>7117590</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568875</v>
+        <v>121568895</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762784</v>
+        <v>762857</v>
       </c>
       <c r="R5" t="n">
-        <v>7117549</v>
+        <v>7117643</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568871</v>
+        <v>121568874</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762884</v>
+        <v>762800</v>
       </c>
       <c r="R7" t="n">
-        <v>7117590</v>
+        <v>7117547</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568872</v>
+        <v>121568876</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762842</v>
+        <v>762743</v>
       </c>
       <c r="R8" t="n">
-        <v>7117580</v>
+        <v>7117540</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568897</v>
+        <v>121568873</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762908</v>
+        <v>762822</v>
       </c>
       <c r="R9" t="n">
-        <v>7117644</v>
+        <v>7117550</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568873</v>
+        <v>121568877</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762822</v>
+        <v>762732</v>
       </c>
       <c r="R10" t="n">
-        <v>7117550</v>
+        <v>7117536</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568898</v>
+        <v>121568897</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762944</v>
+        <v>762908</v>
       </c>
       <c r="R11" t="n">
-        <v>7117656</v>
+        <v>7117644</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568877</v>
+        <v>121568894</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762732</v>
+        <v>762831</v>
       </c>
       <c r="R12" t="n">
-        <v>7117536</v>
+        <v>7117638</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568895</v>
+        <v>121568898</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762857</v>
+        <v>762944</v>
       </c>
       <c r="R13" t="n">
-        <v>7117643</v>
+        <v>7117656</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568872</v>
+        <v>121568871</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762842</v>
+        <v>762884</v>
       </c>
       <c r="R2" t="n">
-        <v>7117580</v>
+        <v>7117590</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568875</v>
+        <v>121568873</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762784</v>
+        <v>762822</v>
       </c>
       <c r="R3" t="n">
-        <v>7117549</v>
+        <v>7117550</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568871</v>
+        <v>121568894</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762884</v>
+        <v>762831</v>
       </c>
       <c r="R4" t="n">
-        <v>7117590</v>
+        <v>7117638</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568895</v>
+        <v>121568874</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762857</v>
+        <v>762800</v>
       </c>
       <c r="R5" t="n">
-        <v>7117643</v>
+        <v>7117547</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568893</v>
+        <v>121568877</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762816</v>
+        <v>762732</v>
       </c>
       <c r="R6" t="n">
-        <v>7117667</v>
+        <v>7117536</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568874</v>
+        <v>121568895</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762800</v>
+        <v>762857</v>
       </c>
       <c r="R7" t="n">
-        <v>7117547</v>
+        <v>7117643</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568876</v>
+        <v>121568897</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762743</v>
+        <v>762908</v>
       </c>
       <c r="R8" t="n">
-        <v>7117540</v>
+        <v>7117644</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568873</v>
+        <v>121568876</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762822</v>
+        <v>762743</v>
       </c>
       <c r="R9" t="n">
-        <v>7117550</v>
+        <v>7117540</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568877</v>
+        <v>121568898</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762732</v>
+        <v>762944</v>
       </c>
       <c r="R10" t="n">
-        <v>7117536</v>
+        <v>7117656</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568897</v>
+        <v>121568875</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762908</v>
+        <v>762784</v>
       </c>
       <c r="R11" t="n">
-        <v>7117644</v>
+        <v>7117549</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568894</v>
+        <v>121568872</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762831</v>
+        <v>762842</v>
       </c>
       <c r="R12" t="n">
-        <v>7117638</v>
+        <v>7117580</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568898</v>
+        <v>121568893</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762944</v>
+        <v>762816</v>
       </c>
       <c r="R13" t="n">
-        <v>7117656</v>
+        <v>7117667</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121568871</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568873</v>
+        <v>121568872</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762822</v>
+        <v>762842</v>
       </c>
       <c r="R3" t="n">
-        <v>7117550</v>
+        <v>7117580</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568894</v>
+        <v>121568873</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762831</v>
+        <v>762822</v>
       </c>
       <c r="R4" t="n">
-        <v>7117638</v>
+        <v>7117550</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,16 +969,11 @@
         <v>121568874</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568877</v>
+        <v>121568875</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762732</v>
+        <v>762784</v>
       </c>
       <c r="R6" t="n">
-        <v>7117536</v>
+        <v>7117549</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568895</v>
+        <v>121568876</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762857</v>
+        <v>762743</v>
       </c>
       <c r="R7" t="n">
-        <v>7117643</v>
+        <v>7117540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568897</v>
+        <v>121568877</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762908</v>
+        <v>762732</v>
       </c>
       <c r="R8" t="n">
-        <v>7117644</v>
+        <v>7117536</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121568876</v>
+        <v>121568893</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762743</v>
+        <v>762816</v>
       </c>
       <c r="R9" t="n">
-        <v>7117540</v>
+        <v>7117667</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121568898</v>
+        <v>121568894</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762944</v>
+        <v>762831</v>
       </c>
       <c r="R10" t="n">
-        <v>7117656</v>
+        <v>7117638</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121568875</v>
+        <v>121568895</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762784</v>
+        <v>762857</v>
       </c>
       <c r="R11" t="n">
-        <v>7117549</v>
+        <v>7117643</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121568872</v>
+        <v>121568897</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762842</v>
+        <v>762908</v>
       </c>
       <c r="R12" t="n">
-        <v>7117580</v>
+        <v>7117644</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568893</v>
+        <v>121568898</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762816</v>
+        <v>762944</v>
       </c>
       <c r="R13" t="n">
-        <v>7117667</v>
+        <v>7117656</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 40665-2024 artfynd.xlsx
+++ b/artfynd/A 40665-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568871</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568873</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568874</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568875</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568877</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568893</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568895</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568897</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,8 +1896,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>